--- a/output/2024/sector_totals_2024.xlsx
+++ b/output/2024/sector_totals_2024.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1622.708316394378</v>
+        <v>1622.708313903729</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>616.9280744662283</v>
+        <v>608.660209163041</v>
       </c>
       <c r="E3" t="n">
-        <v>356.6164544411242</v>
+        <v>357.6466584819659</v>
       </c>
       <c r="F3" t="n">
-        <v>71.49989214802734</v>
+        <v>72.32309226054845</v>
       </c>
       <c r="G3" t="n">
-        <v>4.140809420501751</v>
+        <v>4.108680105024924</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5452.089249291304</v>
+        <v>5452.089246800657</v>
       </c>
       <c r="C16" t="n">
         <v>544.9352086054416</v>
       </c>
       <c r="D16" t="n">
-        <v>3480.954713798887</v>
+        <v>3472.686848495699</v>
       </c>
       <c r="E16" t="n">
-        <v>6690.871137983765</v>
+        <v>6691.901342024607</v>
       </c>
       <c r="F16" t="n">
-        <v>1558.681056429523</v>
+        <v>1559.504256542044</v>
       </c>
       <c r="G16" t="n">
-        <v>28.07940486639828</v>
+        <v>28.04727555092145</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024/sector_totals_2024.xlsx
+++ b/output/2024/sector_totals_2024.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1622.708313903729</v>
+        <v>1722.561925601163</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>608.660209163041</v>
+        <v>680.6951120718549</v>
       </c>
       <c r="E3" t="n">
-        <v>357.6466584819659</v>
+        <v>1949.653090464561</v>
       </c>
       <c r="F3" t="n">
-        <v>72.32309226054845</v>
+        <v>171.9003051692252</v>
       </c>
       <c r="G3" t="n">
-        <v>4.108680105024924</v>
+        <v>76.73608053559714</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5452.089246800657</v>
+        <v>5551.942858498091</v>
       </c>
       <c r="C16" t="n">
         <v>544.9352086054416</v>
       </c>
       <c r="D16" t="n">
-        <v>3472.686848495699</v>
+        <v>3544.721751404513</v>
       </c>
       <c r="E16" t="n">
-        <v>6691.901342024607</v>
+        <v>8283.907774007203</v>
       </c>
       <c r="F16" t="n">
-        <v>1559.504256542044</v>
+        <v>1659.081469450721</v>
       </c>
       <c r="G16" t="n">
-        <v>28.04727555092145</v>
+        <v>100.6746759814937</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024/sector_totals_2024.xlsx
+++ b/output/2024/sector_totals_2024.xlsx
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1722.561925601163</v>
+        <v>1620.133498594501</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>102.4284270066621</v>
       </c>
       <c r="D3" t="n">
         <v>680.6951120718549</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5551.942858498091</v>
+        <v>5449.514431491429</v>
       </c>
       <c r="C16" t="n">
-        <v>544.9352086054416</v>
+        <v>647.3636356121037</v>
       </c>
       <c r="D16" t="n">
         <v>3544.721751404513</v>

--- a/output/2024/sector_totals_2024.xlsx
+++ b/output/2024/sector_totals_2024.xlsx
@@ -467,16 +467,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2118.4</v>
+        <v>2181.7</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>351.284</v>
       </c>
       <c r="D2" t="n">
-        <v>954.9386505477902</v>
+        <v>1055.56</v>
       </c>
       <c r="E2" t="n">
-        <v>86.88444764436542</v>
+        <v>82.23</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1620.133498594501</v>
+        <v>1746.174910787261</v>
       </c>
       <c r="C3" t="n">
-        <v>102.4284270066621</v>
+        <v>114.2272261260875</v>
       </c>
       <c r="D3" t="n">
-        <v>680.6951120718549</v>
+        <v>694.9122369166649</v>
       </c>
       <c r="E3" t="n">
-        <v>1949.653090464561</v>
+        <v>2133.886970859131</v>
       </c>
       <c r="F3" t="n">
-        <v>171.9003051692252</v>
+        <v>183.135460946604</v>
       </c>
       <c r="G3" t="n">
-        <v>76.73608053559714</v>
+        <v>85.25190252231445</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5449.514431491429</v>
+        <v>5638.855843684189</v>
       </c>
       <c r="C16" t="n">
-        <v>647.3636356121037</v>
+        <v>1010.446434731529</v>
       </c>
       <c r="D16" t="n">
-        <v>3544.721751404513</v>
+        <v>3659.560225701533</v>
       </c>
       <c r="E16" t="n">
-        <v>8283.907774007203</v>
+        <v>8463.487206757407</v>
       </c>
       <c r="F16" t="n">
-        <v>1659.081469450721</v>
+        <v>1670.3166252281</v>
       </c>
       <c r="G16" t="n">
-        <v>100.6746759814937</v>
+        <v>109.190497968211</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024/sector_totals_2024.xlsx
+++ b/output/2024/sector_totals_2024.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1746.174910787261</v>
+        <v>1508.300016825448</v>
       </c>
       <c r="C3" t="n">
-        <v>114.2272261260875</v>
+        <v>104.2263884266</v>
       </c>
       <c r="D3" t="n">
-        <v>694.9122369166649</v>
+        <v>602.6188615412943</v>
       </c>
       <c r="E3" t="n">
-        <v>2133.886970859131</v>
+        <v>1924.714465927711</v>
       </c>
       <c r="F3" t="n">
-        <v>183.135460946604</v>
+        <v>160.9516198049996</v>
       </c>
       <c r="G3" t="n">
-        <v>85.25190252231445</v>
+        <v>78.13444760195013</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5638.855843684189</v>
+        <v>5400.980949722376</v>
       </c>
       <c r="C16" t="n">
-        <v>1010.446434731529</v>
+        <v>1000.445597032042</v>
       </c>
       <c r="D16" t="n">
-        <v>3659.560225701533</v>
+        <v>3567.266850326162</v>
       </c>
       <c r="E16" t="n">
-        <v>8463.487206757407</v>
+        <v>8254.314701825988</v>
       </c>
       <c r="F16" t="n">
-        <v>1670.3166252281</v>
+        <v>1648.132784086495</v>
       </c>
       <c r="G16" t="n">
-        <v>109.190497968211</v>
+        <v>102.0730430478467</v>
       </c>
     </row>
   </sheetData>
